--- a/docs/data/beidan_26082_dashboard.xlsx
+++ b/docs/data/beidan_26082_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26082期 比赛看板（皇冠历史相同亚盘） — 2026-08-04</t>
+          <t>⚽ 北京单场26082期 比赛看板（皇冠历史相同亚盘） — 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -644,10 +644,14 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -700,10 +704,14 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -756,10 +764,14 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -812,10 +824,14 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -868,10 +884,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -924,10 +944,14 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="7" t="inlineStr">
         <is>
@@ -976,10 +1000,14 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1476,20 +1504,24 @@
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>31%</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>35%</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -1528,20 +1560,24 @@
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>受半球</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1928,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>08-07 00:00</t>
+          <t>08-07 01:00</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">

--- a/docs/data/beidan_26082_dashboard.xlsx
+++ b/docs/data/beidan_26082_dashboard.xlsx
@@ -142,10 +142,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26082期 比赛看板（皇冠历史相同亚盘） — 2026-08-05</t>
+          <t>⚽ 北京单场26082期 比赛看板（皇冠历史相同亚盘） — 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1060,24 +1060,32 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>34%</t>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>36%</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>34%</t>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>45%</t>
         </is>
       </c>
     </row>
@@ -1112,10 +1120,14 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -1168,10 +1180,14 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1224,10 +1240,14 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1268,7 +1288,7 @@
           <t>哈夫纳夫约杜尔</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
@@ -1280,16 +1300,20 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -1336,10 +1360,14 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1392,10 +1420,14 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
@@ -1444,10 +1476,14 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1500,16 +1536,20 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -1556,10 +1596,14 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -1631,7 +1675,7 @@
           <t>29%</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
@@ -1936,7 +1980,7 @@
           <t>林肯红魔</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
@@ -2048,7 +2092,7 @@
           <t>赫拉德茨</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
@@ -2191,7 +2235,7 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2303,7 +2347,7 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -2415,7 +2459,7 @@
           <t>25%</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="L35" s="8" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -2608,7 +2652,7 @@
           <t>波希米亚人</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
@@ -2741,7 +2785,7 @@
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="J41" s="9" t="inlineStr">
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
@@ -2863,7 +2907,7 @@
           <t>25%</t>
         </is>
       </c>
-      <c r="L43" s="9" t="inlineStr">
+      <c r="L43" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -2960,20 +3004,24 @@
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>28%</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>35%</t>
         </is>
       </c>
     </row>
